--- a/12615817.xlsx
+++ b/12615817.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shashi kumar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E0CC07-0085-4679-AA27-F96E461BB500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -120,6 +118,9 @@
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
+    <t>5. GOOD PRACTICE</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
@@ -186,6 +187,18 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Holiday - no class (weekend).</t>
+  </si>
+  <si>
     <t>Good</t>
   </si>
   <si>
@@ -195,10 +208,22 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
+    <t>Stressed</t>
   </si>
   <si>
-    <t>5. GOOD PRACTICE</t>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Long class day - exhausted by evening.</t>
+  </si>
+  <si>
+    <t>Shashibhushan kumar yadav</t>
+  </si>
+  <si>
+    <t>CAP776</t>
   </si>
 </sst>
 </file>
@@ -664,181 +689,181 @@
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="8"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="7"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="7"/>
     </row>
   </sheetData>
@@ -865,7 +890,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -883,33 +908,39 @@
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="F2" s="2">
+        <v>12615817</v>
+      </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -925,999 +956,1935 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11">
+        <v>46235</v>
+      </c>
+      <c r="B6" s="12">
+        <v>480</v>
+      </c>
+      <c r="C6" s="12">
         <v>40</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="11">
-        <v>46223</v>
-      </c>
-      <c r="B6" s="12">
-        <v>420</v>
-      </c>
-      <c r="C6" s="12">
-        <v>45</v>
-      </c>
       <c r="D6" s="12">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E6" s="12">
+        <v>60</v>
+      </c>
+      <c r="F6" s="12">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12">
         <v>90</v>
-      </c>
-      <c r="F6" s="12">
-        <v>180</v>
-      </c>
-      <c r="G6" s="12">
-        <v>3</v>
-      </c>
-      <c r="H6" s="12">
-        <v>30</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>885</v>
+        <v>730</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
-        <v>555</v>
+        <v>710</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L6" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="16">
+        <v>46236</v>
+      </c>
+      <c r="B7" s="17">
+        <v>480</v>
+      </c>
+      <c r="C7" s="17">
+        <v>40</v>
+      </c>
+      <c r="D7" s="17">
+        <v>60</v>
+      </c>
+      <c r="E7" s="17">
+        <v>60</v>
+      </c>
+      <c r="F7" s="17">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17">
+        <v>0</v>
+      </c>
+      <c r="H7" s="17">
+        <v>90</v>
+      </c>
+      <c r="I7" s="18">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J7" s="18">
+        <f t="shared" si="1"/>
+        <v>710</v>
+      </c>
+      <c r="K7" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="L7" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="15" t="s">
+      <c r="M7" s="19" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18" t="str">
+      <c r="N7" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="16">
+        <v>46237</v>
+      </c>
+      <c r="B8" s="17">
+        <v>420</v>
+      </c>
+      <c r="C8" s="17">
+        <v>45</v>
+      </c>
+      <c r="D8" s="17">
+        <v>90</v>
+      </c>
+      <c r="E8" s="17">
+        <v>90</v>
+      </c>
+      <c r="F8" s="17">
+        <v>180</v>
+      </c>
+      <c r="G8" s="17">
+        <v>3</v>
+      </c>
+      <c r="H8" s="17">
+        <v>45</v>
+      </c>
+      <c r="I8" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J8" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="20"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="20"/>
+    </row>
+    <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="16">
+        <v>46238</v>
+      </c>
+      <c r="B9" s="17">
+        <v>420</v>
+      </c>
+      <c r="C9" s="17">
+        <v>45</v>
+      </c>
+      <c r="D9" s="17">
+        <v>90</v>
+      </c>
+      <c r="E9" s="17">
+        <v>90</v>
+      </c>
+      <c r="F9" s="17">
+        <v>180</v>
+      </c>
+      <c r="G9" s="17">
+        <v>3</v>
+      </c>
+      <c r="H9" s="17">
+        <v>45</v>
+      </c>
+      <c r="I9" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J9" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="20"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="20"/>
+    </row>
+    <row r="10" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="16">
+        <v>46239</v>
+      </c>
+      <c r="B10" s="17">
+        <v>390</v>
+      </c>
+      <c r="C10" s="17">
+        <v>20</v>
+      </c>
+      <c r="D10" s="17">
+        <v>60</v>
+      </c>
+      <c r="E10" s="17">
+        <v>60</v>
+      </c>
+      <c r="F10" s="17">
+        <v>330</v>
+      </c>
+      <c r="G10" s="17">
+        <v>6</v>
+      </c>
+      <c r="H10" s="17">
+        <v>20</v>
+      </c>
+      <c r="I10" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="18" t="str">
+        <v>880</v>
+      </c>
+      <c r="J10" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="20"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="18" t="str">
+        <v>560</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="16">
+        <v>46240</v>
+      </c>
+      <c r="B11" s="17">
+        <v>420</v>
+      </c>
+      <c r="C11" s="17">
+        <v>45</v>
+      </c>
+      <c r="D11" s="17">
+        <v>90</v>
+      </c>
+      <c r="E11" s="17">
+        <v>90</v>
+      </c>
+      <c r="F11" s="17">
+        <v>180</v>
+      </c>
+      <c r="G11" s="17">
+        <v>3</v>
+      </c>
+      <c r="H11" s="17">
+        <v>45</v>
+      </c>
+      <c r="I11" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J11" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="20"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" s="20"/>
+    </row>
+    <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="16">
+        <v>46241</v>
+      </c>
+      <c r="B12" s="17">
+        <v>420</v>
+      </c>
+      <c r="C12" s="17">
+        <v>45</v>
+      </c>
+      <c r="D12" s="17">
+        <v>90</v>
+      </c>
+      <c r="E12" s="17">
+        <v>90</v>
+      </c>
+      <c r="F12" s="17">
+        <v>180</v>
+      </c>
+      <c r="G12" s="17">
+        <v>3</v>
+      </c>
+      <c r="H12" s="17">
+        <v>45</v>
+      </c>
+      <c r="I12" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J12" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="20"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="20"/>
+    </row>
+    <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="16">
+        <v>46242</v>
+      </c>
+      <c r="B13" s="17">
+        <v>480</v>
+      </c>
+      <c r="C13" s="17">
+        <v>40</v>
+      </c>
+      <c r="D13" s="17">
+        <v>60</v>
+      </c>
+      <c r="E13" s="17">
+        <v>60</v>
+      </c>
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="17">
+        <v>90</v>
+      </c>
+      <c r="I13" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="18" t="str">
+        <v>730</v>
+      </c>
+      <c r="J13" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="20"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="18" t="str">
+        <v>710</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N13" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="16">
+        <v>46243</v>
+      </c>
+      <c r="B14" s="17">
+        <v>480</v>
+      </c>
+      <c r="C14" s="17">
+        <v>40</v>
+      </c>
+      <c r="D14" s="17">
+        <v>60</v>
+      </c>
+      <c r="E14" s="17">
+        <v>60</v>
+      </c>
+      <c r="F14" s="17">
+        <v>0</v>
+      </c>
+      <c r="G14" s="17">
+        <v>0</v>
+      </c>
+      <c r="H14" s="17">
+        <v>90</v>
+      </c>
+      <c r="I14" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="18" t="str">
+        <v>730</v>
+      </c>
+      <c r="J14" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="20"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="18" t="str">
+        <v>710</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="16">
+        <v>46244</v>
+      </c>
+      <c r="B15" s="17">
+        <v>420</v>
+      </c>
+      <c r="C15" s="17">
+        <v>45</v>
+      </c>
+      <c r="D15" s="17">
+        <v>90</v>
+      </c>
+      <c r="E15" s="17">
+        <v>90</v>
+      </c>
+      <c r="F15" s="17">
+        <v>180</v>
+      </c>
+      <c r="G15" s="17">
+        <v>3</v>
+      </c>
+      <c r="H15" s="17">
+        <v>45</v>
+      </c>
+      <c r="I15" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J15" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="20"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15" s="20"/>
+    </row>
+    <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="16">
+        <v>46245</v>
+      </c>
+      <c r="B16" s="17">
+        <v>420</v>
+      </c>
+      <c r="C16" s="17">
+        <v>45</v>
+      </c>
+      <c r="D16" s="17">
+        <v>90</v>
+      </c>
+      <c r="E16" s="17">
+        <v>90</v>
+      </c>
+      <c r="F16" s="17">
+        <v>180</v>
+      </c>
+      <c r="G16" s="17">
+        <v>3</v>
+      </c>
+      <c r="H16" s="17">
+        <v>45</v>
+      </c>
+      <c r="I16" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J16" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="20"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="16"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N16" s="20"/>
+    </row>
+    <row r="17" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="16">
+        <v>46246</v>
+      </c>
+      <c r="B17" s="17">
+        <v>390</v>
+      </c>
+      <c r="C17" s="17">
+        <v>20</v>
+      </c>
+      <c r="D17" s="17">
+        <v>60</v>
+      </c>
+      <c r="E17" s="17">
+        <v>60</v>
+      </c>
+      <c r="F17" s="17">
+        <v>330</v>
+      </c>
+      <c r="G17" s="17">
+        <v>6</v>
+      </c>
+      <c r="H17" s="17">
+        <v>20</v>
+      </c>
+      <c r="I17" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="18" t="str">
+        <v>880</v>
+      </c>
+      <c r="J17" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="20"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="18" t="str">
+        <v>560</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="16">
+        <v>46247</v>
+      </c>
+      <c r="B18" s="17">
+        <v>420</v>
+      </c>
+      <c r="C18" s="17">
+        <v>45</v>
+      </c>
+      <c r="D18" s="17">
+        <v>90</v>
+      </c>
+      <c r="E18" s="17">
+        <v>90</v>
+      </c>
+      <c r="F18" s="17">
+        <v>180</v>
+      </c>
+      <c r="G18" s="17">
+        <v>3</v>
+      </c>
+      <c r="H18" s="17">
+        <v>45</v>
+      </c>
+      <c r="I18" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J18" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="20"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="16"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N18" s="20"/>
+    </row>
+    <row r="19" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="16">
+        <v>46248</v>
+      </c>
+      <c r="B19" s="17">
+        <v>420</v>
+      </c>
+      <c r="C19" s="17">
+        <v>45</v>
+      </c>
+      <c r="D19" s="17">
+        <v>90</v>
+      </c>
+      <c r="E19" s="17">
+        <v>90</v>
+      </c>
+      <c r="F19" s="17">
+        <v>180</v>
+      </c>
+      <c r="G19" s="17">
+        <v>3</v>
+      </c>
+      <c r="H19" s="17">
+        <v>45</v>
+      </c>
+      <c r="I19" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J19" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="20"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="16"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N19" s="20"/>
+    </row>
+    <row r="20" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="16">
+        <v>46249</v>
+      </c>
+      <c r="B20" s="17">
+        <v>480</v>
+      </c>
+      <c r="C20" s="17">
+        <v>40</v>
+      </c>
+      <c r="D20" s="17">
+        <v>60</v>
+      </c>
+      <c r="E20" s="17">
+        <v>60</v>
+      </c>
+      <c r="F20" s="17">
+        <v>0</v>
+      </c>
+      <c r="G20" s="17">
+        <v>0</v>
+      </c>
+      <c r="H20" s="17">
+        <v>90</v>
+      </c>
+      <c r="I20" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="18" t="str">
+        <v>730</v>
+      </c>
+      <c r="J20" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="20"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="18" t="str">
+        <v>710</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N20" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="16">
+        <v>46250</v>
+      </c>
+      <c r="B21" s="17">
+        <v>480</v>
+      </c>
+      <c r="C21" s="17">
+        <v>40</v>
+      </c>
+      <c r="D21" s="17">
+        <v>60</v>
+      </c>
+      <c r="E21" s="17">
+        <v>60</v>
+      </c>
+      <c r="F21" s="17">
+        <v>0</v>
+      </c>
+      <c r="G21" s="17">
+        <v>0</v>
+      </c>
+      <c r="H21" s="17">
+        <v>90</v>
+      </c>
+      <c r="I21" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="18" t="str">
+        <v>730</v>
+      </c>
+      <c r="J21" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="20"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="16"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="18" t="str">
+        <v>710</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N21" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="16">
+        <v>46251</v>
+      </c>
+      <c r="B22" s="17">
+        <v>420</v>
+      </c>
+      <c r="C22" s="17">
+        <v>45</v>
+      </c>
+      <c r="D22" s="17">
+        <v>90</v>
+      </c>
+      <c r="E22" s="17">
+        <v>90</v>
+      </c>
+      <c r="F22" s="17">
+        <v>180</v>
+      </c>
+      <c r="G22" s="17">
+        <v>3</v>
+      </c>
+      <c r="H22" s="17">
+        <v>45</v>
+      </c>
+      <c r="I22" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J22" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="20"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="16"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N22" s="20"/>
+    </row>
+    <row r="23" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="16">
+        <v>46252</v>
+      </c>
+      <c r="B23" s="17">
+        <v>420</v>
+      </c>
+      <c r="C23" s="17">
+        <v>45</v>
+      </c>
+      <c r="D23" s="17">
+        <v>90</v>
+      </c>
+      <c r="E23" s="17">
+        <v>90</v>
+      </c>
+      <c r="F23" s="17">
+        <v>180</v>
+      </c>
+      <c r="G23" s="17">
+        <v>3</v>
+      </c>
+      <c r="H23" s="17">
+        <v>45</v>
+      </c>
+      <c r="I23" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J23" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="20"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="16"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M23" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N23" s="20"/>
+    </row>
+    <row r="24" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="16">
+        <v>46253</v>
+      </c>
+      <c r="B24" s="17">
+        <v>390</v>
+      </c>
+      <c r="C24" s="17">
+        <v>20</v>
+      </c>
+      <c r="D24" s="17">
+        <v>60</v>
+      </c>
+      <c r="E24" s="17">
+        <v>60</v>
+      </c>
+      <c r="F24" s="17">
+        <v>330</v>
+      </c>
+      <c r="G24" s="17">
+        <v>6</v>
+      </c>
+      <c r="H24" s="17">
+        <v>20</v>
+      </c>
+      <c r="I24" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="18" t="str">
+        <v>880</v>
+      </c>
+      <c r="J24" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="20"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="16"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="18" t="str">
+        <v>560</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N24" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="16">
+        <v>46254</v>
+      </c>
+      <c r="B25" s="17">
+        <v>420</v>
+      </c>
+      <c r="C25" s="17">
+        <v>45</v>
+      </c>
+      <c r="D25" s="17">
+        <v>90</v>
+      </c>
+      <c r="E25" s="17">
+        <v>90</v>
+      </c>
+      <c r="F25" s="17">
+        <v>180</v>
+      </c>
+      <c r="G25" s="17">
+        <v>3</v>
+      </c>
+      <c r="H25" s="17">
+        <v>45</v>
+      </c>
+      <c r="I25" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J25" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="20"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="16"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L25" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M25" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N25" s="20"/>
+    </row>
+    <row r="26" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="16">
+        <v>46255</v>
+      </c>
+      <c r="B26" s="17">
+        <v>420</v>
+      </c>
+      <c r="C26" s="17">
+        <v>45</v>
+      </c>
+      <c r="D26" s="17">
+        <v>90</v>
+      </c>
+      <c r="E26" s="17">
+        <v>90</v>
+      </c>
+      <c r="F26" s="17">
+        <v>180</v>
+      </c>
+      <c r="G26" s="17">
+        <v>3</v>
+      </c>
+      <c r="H26" s="17">
+        <v>45</v>
+      </c>
+      <c r="I26" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J26" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="20"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="16"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K26" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N26" s="20"/>
+    </row>
+    <row r="27" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="16">
+        <v>46256</v>
+      </c>
+      <c r="B27" s="17">
+        <v>480</v>
+      </c>
+      <c r="C27" s="17">
+        <v>40</v>
+      </c>
+      <c r="D27" s="17">
+        <v>60</v>
+      </c>
+      <c r="E27" s="17">
+        <v>60</v>
+      </c>
+      <c r="F27" s="17">
+        <v>0</v>
+      </c>
+      <c r="G27" s="17">
+        <v>0</v>
+      </c>
+      <c r="H27" s="17">
+        <v>90</v>
+      </c>
+      <c r="I27" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="18" t="str">
+        <v>730</v>
+      </c>
+      <c r="J27" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="20"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="16"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="18" t="str">
+        <v>710</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M27" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N27" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="16">
+        <v>46257</v>
+      </c>
+      <c r="B28" s="17">
+        <v>480</v>
+      </c>
+      <c r="C28" s="17">
+        <v>40</v>
+      </c>
+      <c r="D28" s="17">
+        <v>60</v>
+      </c>
+      <c r="E28" s="17">
+        <v>60</v>
+      </c>
+      <c r="F28" s="17">
+        <v>0</v>
+      </c>
+      <c r="G28" s="17">
+        <v>0</v>
+      </c>
+      <c r="H28" s="17">
+        <v>90</v>
+      </c>
+      <c r="I28" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="18" t="str">
+        <v>730</v>
+      </c>
+      <c r="J28" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="20"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="16"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="18" t="str">
+        <v>710</v>
+      </c>
+      <c r="K28" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M28" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N28" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="16">
+        <v>46258</v>
+      </c>
+      <c r="B29" s="17">
+        <v>420</v>
+      </c>
+      <c r="C29" s="17">
+        <v>45</v>
+      </c>
+      <c r="D29" s="17">
+        <v>90</v>
+      </c>
+      <c r="E29" s="17">
+        <v>90</v>
+      </c>
+      <c r="F29" s="17">
+        <v>180</v>
+      </c>
+      <c r="G29" s="17">
+        <v>3</v>
+      </c>
+      <c r="H29" s="17">
+        <v>45</v>
+      </c>
+      <c r="I29" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J29" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="20"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="16"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K29" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M29" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N29" s="20"/>
+    </row>
+    <row r="30" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="16">
+        <v>46259</v>
+      </c>
+      <c r="B30" s="17">
+        <v>420</v>
+      </c>
+      <c r="C30" s="17">
+        <v>45</v>
+      </c>
+      <c r="D30" s="17">
+        <v>90</v>
+      </c>
+      <c r="E30" s="17">
+        <v>90</v>
+      </c>
+      <c r="F30" s="17">
+        <v>180</v>
+      </c>
+      <c r="G30" s="17">
+        <v>3</v>
+      </c>
+      <c r="H30" s="17">
+        <v>45</v>
+      </c>
+      <c r="I30" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J30" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="20"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="16"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N30" s="20"/>
+    </row>
+    <row r="31" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="16">
+        <v>46260</v>
+      </c>
+      <c r="B31" s="17">
+        <v>390</v>
+      </c>
+      <c r="C31" s="17">
+        <v>20</v>
+      </c>
+      <c r="D31" s="17">
+        <v>60</v>
+      </c>
+      <c r="E31" s="17">
+        <v>60</v>
+      </c>
+      <c r="F31" s="17">
+        <v>330</v>
+      </c>
+      <c r="G31" s="17">
+        <v>6</v>
+      </c>
+      <c r="H31" s="17">
+        <v>20</v>
+      </c>
+      <c r="I31" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="18" t="str">
+        <v>880</v>
+      </c>
+      <c r="J31" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="20"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="16"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="18" t="str">
+        <v>560</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N31" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="16">
+        <v>46261</v>
+      </c>
+      <c r="B32" s="17">
+        <v>420</v>
+      </c>
+      <c r="C32" s="17">
+        <v>45</v>
+      </c>
+      <c r="D32" s="17">
+        <v>90</v>
+      </c>
+      <c r="E32" s="17">
+        <v>90</v>
+      </c>
+      <c r="F32" s="17">
+        <v>180</v>
+      </c>
+      <c r="G32" s="17">
+        <v>3</v>
+      </c>
+      <c r="H32" s="17">
+        <v>45</v>
+      </c>
+      <c r="I32" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J32" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="20"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="16"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M32" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N32" s="20"/>
+    </row>
+    <row r="33" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="16">
+        <v>46262</v>
+      </c>
+      <c r="B33" s="17">
+        <v>420</v>
+      </c>
+      <c r="C33" s="17">
+        <v>45</v>
+      </c>
+      <c r="D33" s="17">
+        <v>90</v>
+      </c>
+      <c r="E33" s="17">
+        <v>90</v>
+      </c>
+      <c r="F33" s="17">
+        <v>180</v>
+      </c>
+      <c r="G33" s="17">
+        <v>3</v>
+      </c>
+      <c r="H33" s="17">
+        <v>45</v>
+      </c>
+      <c r="I33" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J33" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="20"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="16"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K33" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M33" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N33" s="20"/>
+    </row>
+    <row r="34" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="16">
+        <v>46263</v>
+      </c>
+      <c r="B34" s="17">
+        <v>480</v>
+      </c>
+      <c r="C34" s="17">
+        <v>40</v>
+      </c>
+      <c r="D34" s="17">
+        <v>60</v>
+      </c>
+      <c r="E34" s="17">
+        <v>60</v>
+      </c>
+      <c r="F34" s="17">
+        <v>0</v>
+      </c>
+      <c r="G34" s="17">
+        <v>0</v>
+      </c>
+      <c r="H34" s="17">
+        <v>90</v>
+      </c>
+      <c r="I34" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="18" t="str">
+        <v>730</v>
+      </c>
+      <c r="J34" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="20"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="16"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="18" t="str">
+        <v>710</v>
+      </c>
+      <c r="K34" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L34" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M34" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N34" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="16">
+        <v>46264</v>
+      </c>
+      <c r="B35" s="17">
+        <v>480</v>
+      </c>
+      <c r="C35" s="17">
+        <v>40</v>
+      </c>
+      <c r="D35" s="17">
+        <v>60</v>
+      </c>
+      <c r="E35" s="17">
+        <v>60</v>
+      </c>
+      <c r="F35" s="17">
+        <v>0</v>
+      </c>
+      <c r="G35" s="17">
+        <v>0</v>
+      </c>
+      <c r="H35" s="17">
+        <v>90</v>
+      </c>
+      <c r="I35" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="18" t="str">
+        <v>730</v>
+      </c>
+      <c r="J35" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="20"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="16"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="18" t="str">
+        <v>710</v>
+      </c>
+      <c r="K35" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L35" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M35" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N35" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="16">
+        <v>46265</v>
+      </c>
+      <c r="B36" s="17">
+        <v>420</v>
+      </c>
+      <c r="C36" s="17">
+        <v>45</v>
+      </c>
+      <c r="D36" s="17">
+        <v>90</v>
+      </c>
+      <c r="E36" s="17">
+        <v>90</v>
+      </c>
+      <c r="F36" s="17">
+        <v>180</v>
+      </c>
+      <c r="G36" s="17">
+        <v>3</v>
+      </c>
+      <c r="H36" s="17">
+        <v>45</v>
+      </c>
+      <c r="I36" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J36" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="20"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="16"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K36" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L36" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M36" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N36" s="20"/>
+    </row>
+    <row r="37" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="16">
+        <v>46266</v>
+      </c>
+      <c r="B37" s="17">
+        <v>420</v>
+      </c>
+      <c r="C37" s="17">
+        <v>45</v>
+      </c>
+      <c r="D37" s="17">
+        <v>90</v>
+      </c>
+      <c r="E37" s="17">
+        <v>90</v>
+      </c>
+      <c r="F37" s="17">
+        <v>180</v>
+      </c>
+      <c r="G37" s="17">
+        <v>3</v>
+      </c>
+      <c r="H37" s="17">
+        <v>45</v>
+      </c>
+      <c r="I37" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J37" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="20"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="16"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L37" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M37" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N37" s="20"/>
+    </row>
+    <row r="38" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="16">
+        <v>46267</v>
+      </c>
+      <c r="B38" s="17">
+        <v>390</v>
+      </c>
+      <c r="C38" s="17">
+        <v>20</v>
+      </c>
+      <c r="D38" s="17">
+        <v>60</v>
+      </c>
+      <c r="E38" s="17">
+        <v>60</v>
+      </c>
+      <c r="F38" s="17">
+        <v>330</v>
+      </c>
+      <c r="G38" s="17">
+        <v>6</v>
+      </c>
+      <c r="H38" s="17">
+        <v>20</v>
+      </c>
+      <c r="I38" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="18" t="str">
+        <v>880</v>
+      </c>
+      <c r="J38" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="20"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="16"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="18" t="str">
+        <v>560</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="L38" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M38" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N38" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="16">
+        <v>46268</v>
+      </c>
+      <c r="B39" s="17">
+        <v>420</v>
+      </c>
+      <c r="C39" s="17">
+        <v>45</v>
+      </c>
+      <c r="D39" s="17">
+        <v>90</v>
+      </c>
+      <c r="E39" s="17">
+        <v>90</v>
+      </c>
+      <c r="F39" s="17">
+        <v>180</v>
+      </c>
+      <c r="G39" s="17">
+        <v>3</v>
+      </c>
+      <c r="H39" s="17">
+        <v>45</v>
+      </c>
+      <c r="I39" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J39" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="20"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="16"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M39" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N39" s="20"/>
+    </row>
+    <row r="40" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="16">
+        <v>46269</v>
+      </c>
+      <c r="B40" s="17">
+        <v>420</v>
+      </c>
+      <c r="C40" s="17">
+        <v>45</v>
+      </c>
+      <c r="D40" s="17">
+        <v>90</v>
+      </c>
+      <c r="E40" s="17">
+        <v>90</v>
+      </c>
+      <c r="F40" s="17">
+        <v>180</v>
+      </c>
+      <c r="G40" s="17">
+        <v>3</v>
+      </c>
+      <c r="H40" s="17">
+        <v>45</v>
+      </c>
+      <c r="I40" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J40" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="20"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="16"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K40" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L40" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M40" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N40" s="20"/>
+    </row>
+    <row r="41" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="16">
+        <v>46270</v>
+      </c>
+      <c r="B41" s="17">
+        <v>480</v>
+      </c>
+      <c r="C41" s="17">
+        <v>40</v>
+      </c>
+      <c r="D41" s="17">
+        <v>60</v>
+      </c>
+      <c r="E41" s="17">
+        <v>60</v>
+      </c>
+      <c r="F41" s="17">
+        <v>0</v>
+      </c>
+      <c r="G41" s="17">
+        <v>0</v>
+      </c>
+      <c r="H41" s="17">
+        <v>90</v>
+      </c>
+      <c r="I41" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="18" t="str">
+        <v>730</v>
+      </c>
+      <c r="J41" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="20"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="16"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="18" t="str">
+        <v>710</v>
+      </c>
+      <c r="K41" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L41" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M41" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N41" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="16">
+        <v>46271</v>
+      </c>
+      <c r="B42" s="17">
+        <v>480</v>
+      </c>
+      <c r="C42" s="17">
+        <v>40</v>
+      </c>
+      <c r="D42" s="17">
+        <v>60</v>
+      </c>
+      <c r="E42" s="17">
+        <v>60</v>
+      </c>
+      <c r="F42" s="17">
+        <v>0</v>
+      </c>
+      <c r="G42" s="17">
+        <v>0</v>
+      </c>
+      <c r="H42" s="17">
+        <v>90</v>
+      </c>
+      <c r="I42" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="18" t="str">
+        <v>730</v>
+      </c>
+      <c r="J42" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="20"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="16"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="18" t="str">
+        <v>710</v>
+      </c>
+      <c r="K42" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L42" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M42" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N42" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="16">
+        <v>46272</v>
+      </c>
+      <c r="B43" s="17">
+        <v>420</v>
+      </c>
+      <c r="C43" s="17">
+        <v>45</v>
+      </c>
+      <c r="D43" s="17">
+        <v>90</v>
+      </c>
+      <c r="E43" s="17">
+        <v>90</v>
+      </c>
+      <c r="F43" s="17">
+        <v>180</v>
+      </c>
+      <c r="G43" s="17">
+        <v>3</v>
+      </c>
+      <c r="H43" s="17">
+        <v>45</v>
+      </c>
+      <c r="I43" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J43" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="20"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="16"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K43" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L43" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M43" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N43" s="20"/>
+    </row>
+    <row r="44" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="16">
+        <v>46273</v>
+      </c>
+      <c r="B44" s="17">
+        <v>420</v>
+      </c>
+      <c r="C44" s="17">
+        <v>45</v>
+      </c>
+      <c r="D44" s="17">
+        <v>90</v>
+      </c>
+      <c r="E44" s="17">
+        <v>90</v>
+      </c>
+      <c r="F44" s="17">
+        <v>180</v>
+      </c>
+      <c r="G44" s="17">
+        <v>3</v>
+      </c>
+      <c r="H44" s="17">
+        <v>45</v>
+      </c>
+      <c r="I44" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J44" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="20"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="16"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K44" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L44" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M44" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N44" s="20"/>
+    </row>
+    <row r="45" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="16">
+        <v>46274</v>
+      </c>
+      <c r="B45" s="17">
+        <v>390</v>
+      </c>
+      <c r="C45" s="17">
+        <v>20</v>
+      </c>
+      <c r="D45" s="17">
+        <v>60</v>
+      </c>
+      <c r="E45" s="17">
+        <v>60</v>
+      </c>
+      <c r="F45" s="17">
+        <v>330</v>
+      </c>
+      <c r="G45" s="17">
+        <v>6</v>
+      </c>
+      <c r="H45" s="17">
+        <v>20</v>
+      </c>
+      <c r="I45" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="18" t="str">
+        <v>880</v>
+      </c>
+      <c r="J45" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="20"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="16"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="18" t="str">
+        <v>560</v>
+      </c>
+      <c r="K45" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="L45" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M45" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N45" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="16">
+        <v>46275</v>
+      </c>
+      <c r="B46" s="17">
+        <v>420</v>
+      </c>
+      <c r="C46" s="17">
+        <v>45</v>
+      </c>
+      <c r="D46" s="17">
+        <v>90</v>
+      </c>
+      <c r="E46" s="17">
+        <v>90</v>
+      </c>
+      <c r="F46" s="17">
+        <v>180</v>
+      </c>
+      <c r="G46" s="17">
+        <v>3</v>
+      </c>
+      <c r="H46" s="17">
+        <v>45</v>
+      </c>
+      <c r="I46" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J46" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="20"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="16"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="18" t="str">
+        <v>570</v>
+      </c>
+      <c r="K46" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L46" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M46" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N46" s="20"/>
+    </row>
+    <row r="47" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="16">
+        <v>46276</v>
+      </c>
+      <c r="B47" s="17">
+        <v>420</v>
+      </c>
+      <c r="C47" s="17">
+        <v>45</v>
+      </c>
+      <c r="D47" s="17">
+        <v>90</v>
+      </c>
+      <c r="E47" s="17">
+        <v>90</v>
+      </c>
+      <c r="F47" s="17">
+        <v>180</v>
+      </c>
+      <c r="G47" s="17">
+        <v>3</v>
+      </c>
+      <c r="H47" s="17">
+        <v>45</v>
+      </c>
+      <c r="I47" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="18" t="str">
+        <v>870</v>
+      </c>
+      <c r="J47" s="18">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="19"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="20"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="16"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
+        <v>570</v>
+      </c>
+      <c r="K47" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L47" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M47" s="19" t="s">
+        <v>56</v>
+      </c>
       <c r="N47" s="20"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="16"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -1939,7 +2906,7 @@
       <c r="M48" s="19"/>
       <c r="N48" s="20"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="16"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -1961,7 +2928,7 @@
       <c r="M49" s="19"/>
       <c r="N49" s="20"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="16"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -1983,7 +2950,7 @@
       <c r="M50" s="19"/>
       <c r="N50" s="20"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="16"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -2005,7 +2972,7 @@
       <c r="M51" s="19"/>
       <c r="N51" s="20"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="16"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -2027,7 +2994,7 @@
       <c r="M52" s="19"/>
       <c r="N52" s="20"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="16"/>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -2049,7 +3016,7 @@
       <c r="M53" s="19"/>
       <c r="N53" s="20"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="16"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -2071,7 +3038,7 @@
       <c r="M54" s="19"/>
       <c r="N54" s="20"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="16"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -2093,7 +3060,7 @@
       <c r="M55" s="19"/>
       <c r="N55" s="20"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="16"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -2115,7 +3082,7 @@
       <c r="M56" s="19"/>
       <c r="N56" s="20"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="16"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -2137,7 +3104,7 @@
       <c r="M57" s="19"/>
       <c r="N57" s="20"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="16"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -2159,7 +3126,7 @@
       <c r="M58" s="19"/>
       <c r="N58" s="20"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="16"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -2181,7 +3148,7 @@
       <c r="M59" s="19"/>
       <c r="N59" s="20"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="16"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -2203,7 +3170,7 @@
       <c r="M60" s="19"/>
       <c r="N60" s="20"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="16"/>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
@@ -2225,7 +3192,7 @@
       <c r="M61" s="19"/>
       <c r="N61" s="20"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="16"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -2247,7 +3214,7 @@
       <c r="M62" s="19"/>
       <c r="N62" s="20"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="16"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -2269,7 +3236,7 @@
       <c r="M63" s="19"/>
       <c r="N63" s="20"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="16"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -2291,7 +3258,7 @@
       <c r="M64" s="19"/>
       <c r="N64" s="20"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="16"/>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
@@ -2313,7 +3280,7 @@
       <c r="M65" s="19"/>
       <c r="N65" s="20"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="16"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -2335,7 +3302,7 @@
       <c r="M66" s="19"/>
       <c r="N66" s="20"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="16"/>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -2357,7 +3324,7 @@
       <c r="M67" s="19"/>
       <c r="N67" s="20"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="16"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -2379,7 +3346,7 @@
       <c r="M68" s="19"/>
       <c r="N68" s="20"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="16"/>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
@@ -2401,7 +3368,7 @@
       <c r="M69" s="19"/>
       <c r="N69" s="20"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="16"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -2423,7 +3390,7 @@
       <c r="M70" s="19"/>
       <c r="N70" s="20"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="16"/>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
@@ -2445,7 +3412,7 @@
       <c r="M71" s="19"/>
       <c r="N71" s="20"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="16"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -2467,7 +3434,7 @@
       <c r="M72" s="19"/>
       <c r="N72" s="20"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="16"/>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
@@ -2489,7 +3456,7 @@
       <c r="M73" s="19"/>
       <c r="N73" s="20"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="16"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -2511,7 +3478,7 @@
       <c r="M74" s="19"/>
       <c r="N74" s="20"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="16"/>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
@@ -2533,7 +3500,7 @@
       <c r="M75" s="19"/>
       <c r="N75" s="20"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="16"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -2555,7 +3522,7 @@
       <c r="M76" s="19"/>
       <c r="N76" s="20"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="16"/>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
@@ -2577,7 +3544,7 @@
       <c r="M77" s="19"/>
       <c r="N77" s="20"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="16"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -2599,7 +3566,7 @@
       <c r="M78" s="19"/>
       <c r="N78" s="20"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="16"/>
       <c r="B79" s="17"/>
       <c r="C79" s="17"/>
@@ -2621,7 +3588,7 @@
       <c r="M79" s="19"/>
       <c r="N79" s="20"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="16"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -2643,7 +3610,7 @@
       <c r="M80" s="19"/>
       <c r="N80" s="20"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="16"/>
       <c r="B81" s="17"/>
       <c r="C81" s="17"/>
@@ -2665,7 +3632,7 @@
       <c r="M81" s="19"/>
       <c r="N81" s="20"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="16"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -2687,7 +3654,7 @@
       <c r="M82" s="19"/>
       <c r="N82" s="20"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="16"/>
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
@@ -2709,7 +3676,7 @@
       <c r="M83" s="19"/>
       <c r="N83" s="20"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="16"/>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -2731,7 +3698,7 @@
       <c r="M84" s="19"/>
       <c r="N84" s="20"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="16"/>
       <c r="B85" s="17"/>
       <c r="C85" s="17"/>
@@ -2753,7 +3720,7 @@
       <c r="M85" s="19"/>
       <c r="N85" s="20"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="16"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -2775,7 +3742,7 @@
       <c r="M86" s="19"/>
       <c r="N86" s="20"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="16"/>
       <c r="B87" s="17"/>
       <c r="C87" s="17"/>
@@ -2797,7 +3764,7 @@
       <c r="M87" s="19"/>
       <c r="N87" s="20"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="16"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -2819,7 +3786,7 @@
       <c r="M88" s="19"/>
       <c r="N88" s="20"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="16"/>
       <c r="B89" s="17"/>
       <c r="C89" s="17"/>
@@ -2841,7 +3808,7 @@
       <c r="M89" s="19"/>
       <c r="N89" s="20"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="16"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -2863,7 +3830,7 @@
       <c r="M90" s="19"/>
       <c r="N90" s="20"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="16"/>
       <c r="B91" s="17"/>
       <c r="C91" s="17"/>
@@ -2885,7 +3852,7 @@
       <c r="M91" s="19"/>
       <c r="N91" s="20"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="16"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -2907,7 +3874,7 @@
       <c r="M92" s="19"/>
       <c r="N92" s="20"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="16"/>
       <c r="B93" s="17"/>
       <c r="C93" s="17"/>
@@ -2929,7 +3896,7 @@
       <c r="M93" s="19"/>
       <c r="N93" s="20"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="16"/>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -2951,7 +3918,7 @@
       <c r="M94" s="19"/>
       <c r="N94" s="20"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="16"/>
       <c r="B95" s="17"/>
       <c r="C95" s="17"/>
@@ -2973,7 +3940,7 @@
       <c r="M95" s="19"/>
       <c r="N95" s="20"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="16"/>
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
@@ -2995,7 +3962,7 @@
       <c r="M96" s="19"/>
       <c r="N96" s="20"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="16"/>
       <c r="B97" s="17"/>
       <c r="C97" s="17"/>
@@ -3017,7 +3984,7 @@
       <c r="M97" s="19"/>
       <c r="N97" s="20"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="16"/>
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
@@ -3039,7 +4006,7 @@
       <c r="M98" s="19"/>
       <c r="N98" s="20"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="16"/>
       <c r="B99" s="17"/>
       <c r="C99" s="17"/>
@@ -3061,7 +4028,7 @@
       <c r="M99" s="19"/>
       <c r="N99" s="20"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="16"/>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -3083,7 +4050,7 @@
       <c r="M100" s="19"/>
       <c r="N100" s="20"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="16"/>
       <c r="B101" s="17"/>
       <c r="C101" s="17"/>
@@ -3105,7 +4072,7 @@
       <c r="M101" s="19"/>
       <c r="N101" s="20"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="16"/>
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
@@ -3127,7 +4094,7 @@
       <c r="M102" s="19"/>
       <c r="N102" s="20"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="16"/>
       <c r="B103" s="17"/>
       <c r="C103" s="17"/>
@@ -3149,7 +4116,7 @@
       <c r="M103" s="19"/>
       <c r="N103" s="20"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="16"/>
       <c r="B104" s="17"/>
       <c r="C104" s="17"/>
@@ -3171,7 +4138,7 @@
       <c r="M104" s="19"/>
       <c r="N104" s="20"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="16"/>
       <c r="B105" s="17"/>
       <c r="C105" s="17"/>
@@ -3193,7 +4160,7 @@
       <c r="M105" s="19"/>
       <c r="N105" s="20"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="16"/>
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
@@ -3215,7 +4182,7 @@
       <c r="M106" s="19"/>
       <c r="N106" s="20"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="16"/>
       <c r="B107" s="17"/>
       <c r="C107" s="17"/>
@@ -3237,7 +4204,7 @@
       <c r="M107" s="19"/>
       <c r="N107" s="20"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="16"/>
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
@@ -3259,7 +4226,7 @@
       <c r="M108" s="19"/>
       <c r="N108" s="20"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="16"/>
       <c r="B109" s="17"/>
       <c r="C109" s="17"/>
@@ -3281,7 +4248,7 @@
       <c r="M109" s="19"/>
       <c r="N109" s="20"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="16"/>
       <c r="B110" s="17"/>
       <c r="C110" s="17"/>
@@ -3303,7 +4270,7 @@
       <c r="M110" s="19"/>
       <c r="N110" s="20"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="16"/>
       <c r="B111" s="17"/>
       <c r="C111" s="17"/>
@@ -3325,7 +4292,7 @@
       <c r="M111" s="19"/>
       <c r="N111" s="20"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="16"/>
       <c r="B112" s="17"/>
       <c r="C112" s="17"/>
@@ -3347,7 +4314,7 @@
       <c r="M112" s="19"/>
       <c r="N112" s="20"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="16"/>
       <c r="B113" s="17"/>
       <c r="C113" s="17"/>
@@ -3369,7 +4336,7 @@
       <c r="M113" s="19"/>
       <c r="N113" s="20"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="16"/>
       <c r="B114" s="17"/>
       <c r="C114" s="17"/>
@@ -3391,7 +4358,7 @@
       <c r="M114" s="19"/>
       <c r="N114" s="20"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="16"/>
       <c r="B115" s="17"/>
       <c r="C115" s="17"/>
@@ -3413,7 +4380,7 @@
       <c r="M115" s="19"/>
       <c r="N115" s="20"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="16"/>
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
@@ -3435,7 +4402,7 @@
       <c r="M116" s="19"/>
       <c r="N116" s="20"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="16"/>
       <c r="B117" s="17"/>
       <c r="C117" s="17"/>
@@ -3457,7 +4424,7 @@
       <c r="M117" s="19"/>
       <c r="N117" s="20"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="16"/>
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
@@ -3479,7 +4446,7 @@
       <c r="M118" s="19"/>
       <c r="N118" s="20"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="16"/>
       <c r="B119" s="17"/>
       <c r="C119" s="17"/>
@@ -3501,7 +4468,7 @@
       <c r="M119" s="19"/>
       <c r="N119" s="20"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="16"/>
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
@@ -3523,7 +4490,7 @@
       <c r="M120" s="19"/>
       <c r="N120" s="20"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="16"/>
       <c r="B121" s="17"/>
       <c r="C121" s="17"/>
@@ -3545,7 +4512,7 @@
       <c r="M121" s="19"/>
       <c r="N121" s="20"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="16"/>
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
@@ -3567,7 +4534,7 @@
       <c r="M122" s="19"/>
       <c r="N122" s="20"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="16"/>
       <c r="B123" s="17"/>
       <c r="C123" s="17"/>
@@ -3589,7 +4556,7 @@
       <c r="M123" s="19"/>
       <c r="N123" s="20"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="16"/>
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
@@ -3611,7 +4578,7 @@
       <c r="M124" s="19"/>
       <c r="N124" s="20"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="16"/>
       <c r="B125" s="17"/>
       <c r="C125" s="17"/>
@@ -3633,7 +4600,7 @@
       <c r="M125" s="19"/>
       <c r="N125" s="20"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="16"/>
       <c r="B126" s="17"/>
       <c r="C126" s="17"/>
@@ -3655,7 +4622,7 @@
       <c r="M126" s="19"/>
       <c r="N126" s="20"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="16"/>
       <c r="B127" s="17"/>
       <c r="C127" s="17"/>
@@ -3677,7 +4644,7 @@
       <c r="M127" s="19"/>
       <c r="N127" s="20"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="16"/>
       <c r="B128" s="17"/>
       <c r="C128" s="17"/>
@@ -3699,7 +4666,7 @@
       <c r="M128" s="19"/>
       <c r="N128" s="20"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="16"/>
       <c r="B129" s="17"/>
       <c r="C129" s="17"/>
@@ -3721,7 +4688,7 @@
       <c r="M129" s="19"/>
       <c r="N129" s="20"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="16"/>
       <c r="B130" s="17"/>
       <c r="C130" s="17"/>
@@ -3743,7 +4710,7 @@
       <c r="M130" s="19"/>
       <c r="N130" s="20"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="16"/>
       <c r="B131" s="17"/>
       <c r="C131" s="17"/>
@@ -3765,7 +4732,7 @@
       <c r="M131" s="19"/>
       <c r="N131" s="20"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="16"/>
       <c r="B132" s="17"/>
       <c r="C132" s="17"/>
@@ -3787,7 +4754,7 @@
       <c r="M132" s="19"/>
       <c r="N132" s="20"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="16"/>
       <c r="B133" s="17"/>
       <c r="C133" s="17"/>
@@ -3809,7 +4776,7 @@
       <c r="M133" s="19"/>
       <c r="N133" s="20"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="16"/>
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
@@ -3831,7 +4798,7 @@
       <c r="M134" s="19"/>
       <c r="N134" s="20"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="16"/>
       <c r="B135" s="17"/>
       <c r="C135" s="17"/>
@@ -3853,7 +4820,7 @@
       <c r="M135" s="19"/>
       <c r="N135" s="20"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="16"/>
       <c r="B136" s="17"/>
       <c r="C136" s="17"/>
@@ -3875,7 +4842,7 @@
       <c r="M136" s="19"/>
       <c r="N136" s="20"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="16"/>
       <c r="B137" s="17"/>
       <c r="C137" s="17"/>
@@ -3897,7 +4864,7 @@
       <c r="M137" s="19"/>
       <c r="N137" s="20"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="16"/>
       <c r="B138" s="17"/>
       <c r="C138" s="17"/>
@@ -3919,7 +4886,7 @@
       <c r="M138" s="19"/>
       <c r="N138" s="20"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="16"/>
       <c r="B139" s="17"/>
       <c r="C139" s="17"/>
@@ -3941,7 +4908,7 @@
       <c r="M139" s="19"/>
       <c r="N139" s="20"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="16"/>
       <c r="B140" s="17"/>
       <c r="C140" s="17"/>
@@ -3963,7 +4930,7 @@
       <c r="M140" s="19"/>
       <c r="N140" s="20"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="16"/>
       <c r="B141" s="17"/>
       <c r="C141" s="17"/>
@@ -3985,7 +4952,7 @@
       <c r="M141" s="19"/>
       <c r="N141" s="20"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="16"/>
       <c r="B142" s="17"/>
       <c r="C142" s="17"/>
@@ -4007,7 +4974,7 @@
       <c r="M142" s="19"/>
       <c r="N142" s="20"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="16"/>
       <c r="B143" s="17"/>
       <c r="C143" s="17"/>
@@ -4029,7 +4996,7 @@
       <c r="M143" s="19"/>
       <c r="N143" s="20"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="16"/>
       <c r="B144" s="17"/>
       <c r="C144" s="17"/>
@@ -4051,7 +5018,7 @@
       <c r="M144" s="19"/>
       <c r="N144" s="20"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="16"/>
       <c r="B145" s="17"/>
       <c r="C145" s="17"/>
@@ -4073,7 +5040,7 @@
       <c r="M145" s="19"/>
       <c r="N145" s="20"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="16"/>
       <c r="B146" s="17"/>
       <c r="C146" s="17"/>
@@ -4095,7 +5062,7 @@
       <c r="M146" s="19"/>
       <c r="N146" s="20"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="16"/>
       <c r="B147" s="17"/>
       <c r="C147" s="17"/>
@@ -4117,7 +5084,7 @@
       <c r="M147" s="19"/>
       <c r="N147" s="20"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="16"/>
       <c r="B148" s="17"/>
       <c r="C148" s="17"/>
@@ -4139,7 +5106,7 @@
       <c r="M148" s="19"/>
       <c r="N148" s="20"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="16"/>
       <c r="B149" s="17"/>
       <c r="C149" s="17"/>
@@ -4161,7 +5128,7 @@
       <c r="M149" s="19"/>
       <c r="N149" s="20"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="16"/>
       <c r="B150" s="17"/>
       <c r="C150" s="17"/>
@@ -4183,7 +5150,7 @@
       <c r="M150" s="19"/>
       <c r="N150" s="20"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="16"/>
       <c r="B151" s="17"/>
       <c r="C151" s="17"/>
@@ -4205,7 +5172,7 @@
       <c r="M151" s="19"/>
       <c r="N151" s="20"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="16"/>
       <c r="B152" s="17"/>
       <c r="C152" s="17"/>
@@ -4227,7 +5194,7 @@
       <c r="M152" s="19"/>
       <c r="N152" s="20"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="16"/>
       <c r="B153" s="17"/>
       <c r="C153" s="17"/>
@@ -4249,7 +5216,7 @@
       <c r="M153" s="19"/>
       <c r="N153" s="20"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="16"/>
       <c r="B154" s="17"/>
       <c r="C154" s="17"/>
@@ -4271,7 +5238,7 @@
       <c r="M154" s="19"/>
       <c r="N154" s="20"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="16"/>
       <c r="B155" s="17"/>
       <c r="C155" s="17"/>
@@ -4293,7 +5260,7 @@
       <c r="M155" s="19"/>
       <c r="N155" s="20"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="16"/>
       <c r="B156" s="17"/>
       <c r="C156" s="17"/>
@@ -4315,7 +5282,7 @@
       <c r="M156" s="19"/>
       <c r="N156" s="20"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="16"/>
       <c r="B157" s="17"/>
       <c r="C157" s="17"/>
@@ -4337,7 +5304,7 @@
       <c r="M157" s="19"/>
       <c r="N157" s="20"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="16"/>
       <c r="B158" s="17"/>
       <c r="C158" s="17"/>
@@ -4359,7 +5326,7 @@
       <c r="M158" s="19"/>
       <c r="N158" s="20"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="16"/>
       <c r="B159" s="17"/>
       <c r="C159" s="17"/>
@@ -4381,7 +5348,7 @@
       <c r="M159" s="19"/>
       <c r="N159" s="20"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="16"/>
       <c r="B160" s="17"/>
       <c r="C160" s="17"/>
@@ -4403,7 +5370,7 @@
       <c r="M160" s="19"/>
       <c r="N160" s="20"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="16"/>
       <c r="B161" s="17"/>
       <c r="C161" s="17"/>
@@ -4425,7 +5392,7 @@
       <c r="M161" s="19"/>
       <c r="N161" s="20"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="16"/>
       <c r="B162" s="17"/>
       <c r="C162" s="17"/>
@@ -4447,7 +5414,7 @@
       <c r="M162" s="19"/>
       <c r="N162" s="20"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="16"/>
       <c r="B163" s="17"/>
       <c r="C163" s="17"/>
@@ -4469,7 +5436,7 @@
       <c r="M163" s="19"/>
       <c r="N163" s="20"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="16"/>
       <c r="B164" s="17"/>
       <c r="C164" s="17"/>
@@ -4491,7 +5458,7 @@
       <c r="M164" s="19"/>
       <c r="N164" s="20"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="16"/>
       <c r="B165" s="17"/>
       <c r="C165" s="17"/>
@@ -4513,7 +5480,7 @@
       <c r="M165" s="19"/>
       <c r="N165" s="20"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="16"/>
       <c r="B166" s="17"/>
       <c r="C166" s="17"/>
@@ -4535,7 +5502,7 @@
       <c r="M166" s="19"/>
       <c r="N166" s="20"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="16"/>
       <c r="B167" s="17"/>
       <c r="C167" s="17"/>
@@ -4557,7 +5524,7 @@
       <c r="M167" s="19"/>
       <c r="N167" s="20"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="16"/>
       <c r="B168" s="17"/>
       <c r="C168" s="17"/>
@@ -4579,7 +5546,7 @@
       <c r="M168" s="19"/>
       <c r="N168" s="20"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="16"/>
       <c r="B169" s="17"/>
       <c r="C169" s="17"/>
@@ -4601,7 +5568,7 @@
       <c r="M169" s="19"/>
       <c r="N169" s="20"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="16"/>
       <c r="B170" s="17"/>
       <c r="C170" s="17"/>
@@ -4623,7 +5590,7 @@
       <c r="M170" s="19"/>
       <c r="N170" s="20"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="16"/>
       <c r="B171" s="17"/>
       <c r="C171" s="17"/>
@@ -4645,7 +5612,7 @@
       <c r="M171" s="19"/>
       <c r="N171" s="20"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="16"/>
       <c r="B172" s="17"/>
       <c r="C172" s="17"/>
@@ -4667,7 +5634,7 @@
       <c r="M172" s="19"/>
       <c r="N172" s="20"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="16"/>
       <c r="B173" s="17"/>
       <c r="C173" s="17"/>
@@ -4689,7 +5656,7 @@
       <c r="M173" s="19"/>
       <c r="N173" s="20"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="16"/>
       <c r="B174" s="17"/>
       <c r="C174" s="17"/>
@@ -4711,7 +5678,7 @@
       <c r="M174" s="19"/>
       <c r="N174" s="20"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="16"/>
       <c r="B175" s="17"/>
       <c r="C175" s="17"/>
@@ -4733,7 +5700,7 @@
       <c r="M175" s="19"/>
       <c r="N175" s="20"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="16"/>
       <c r="B176" s="17"/>
       <c r="C176" s="17"/>
@@ -4755,7 +5722,7 @@
       <c r="M176" s="19"/>
       <c r="N176" s="20"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="16"/>
       <c r="B177" s="17"/>
       <c r="C177" s="17"/>
@@ -4777,7 +5744,7 @@
       <c r="M177" s="19"/>
       <c r="N177" s="20"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="16"/>
       <c r="B178" s="17"/>
       <c r="C178" s="17"/>
@@ -4799,7 +5766,7 @@
       <c r="M178" s="19"/>
       <c r="N178" s="20"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="16"/>
       <c r="B179" s="17"/>
       <c r="C179" s="17"/>
@@ -4821,7 +5788,7 @@
       <c r="M179" s="19"/>
       <c r="N179" s="20"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="16"/>
       <c r="B180" s="17"/>
       <c r="C180" s="17"/>
@@ -4843,7 +5810,7 @@
       <c r="M180" s="19"/>
       <c r="N180" s="20"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="16"/>
       <c r="B181" s="17"/>
       <c r="C181" s="17"/>
@@ -4865,7 +5832,7 @@
       <c r="M181" s="19"/>
       <c r="N181" s="20"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="16"/>
       <c r="B182" s="17"/>
       <c r="C182" s="17"/>
@@ -4887,7 +5854,7 @@
       <c r="M182" s="19"/>
       <c r="N182" s="20"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="16"/>
       <c r="B183" s="17"/>
       <c r="C183" s="17"/>
@@ -4909,7 +5876,7 @@
       <c r="M183" s="19"/>
       <c r="N183" s="20"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="16"/>
       <c r="B184" s="17"/>
       <c r="C184" s="17"/>
@@ -4931,7 +5898,7 @@
       <c r="M184" s="19"/>
       <c r="N184" s="20"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="16"/>
       <c r="B185" s="17"/>
       <c r="C185" s="17"/>
@@ -4953,7 +5920,7 @@
       <c r="M185" s="19"/>
       <c r="N185" s="20"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="16"/>
       <c r="B186" s="17"/>
       <c r="C186" s="17"/>
@@ -4975,7 +5942,7 @@
       <c r="M186" s="19"/>
       <c r="N186" s="20"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="16"/>
       <c r="B187" s="17"/>
       <c r="C187" s="17"/>
@@ -4997,7 +5964,7 @@
       <c r="M187" s="19"/>
       <c r="N187" s="20"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="16"/>
       <c r="B188" s="17"/>
       <c r="C188" s="17"/>
@@ -5019,7 +5986,7 @@
       <c r="M188" s="19"/>
       <c r="N188" s="20"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="16"/>
       <c r="B189" s="17"/>
       <c r="C189" s="17"/>
@@ -5041,7 +6008,7 @@
       <c r="M189" s="19"/>
       <c r="N189" s="20"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="16"/>
       <c r="B190" s="17"/>
       <c r="C190" s="17"/>
@@ -5063,7 +6030,7 @@
       <c r="M190" s="19"/>
       <c r="N190" s="20"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="16"/>
       <c r="B191" s="17"/>
       <c r="C191" s="17"/>
@@ -5085,7 +6052,7 @@
       <c r="M191" s="19"/>
       <c r="N191" s="20"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="16"/>
       <c r="B192" s="17"/>
       <c r="C192" s="17"/>
@@ -5107,7 +6074,7 @@
       <c r="M192" s="19"/>
       <c r="N192" s="20"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="16"/>
       <c r="B193" s="17"/>
       <c r="C193" s="17"/>
@@ -5129,7 +6096,7 @@
       <c r="M193" s="19"/>
       <c r="N193" s="20"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="16"/>
       <c r="B194" s="17"/>
       <c r="C194" s="17"/>
@@ -5151,7 +6118,7 @@
       <c r="M194" s="19"/>
       <c r="N194" s="20"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="16"/>
       <c r="B195" s="17"/>
       <c r="C195" s="17"/>
@@ -5173,7 +6140,7 @@
       <c r="M195" s="19"/>
       <c r="N195" s="20"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="16"/>
       <c r="B196" s="17"/>
       <c r="C196" s="17"/>
@@ -5195,7 +6162,7 @@
       <c r="M196" s="19"/>
       <c r="N196" s="20"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="16"/>
       <c r="B197" s="17"/>
       <c r="C197" s="17"/>
@@ -5217,7 +6184,7 @@
       <c r="M197" s="19"/>
       <c r="N197" s="20"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="16"/>
       <c r="B198" s="17"/>
       <c r="C198" s="17"/>
@@ -5239,7 +6206,7 @@
       <c r="M198" s="19"/>
       <c r="N198" s="20"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="16"/>
       <c r="B199" s="17"/>
       <c r="C199" s="17"/>
@@ -5261,7 +6228,7 @@
       <c r="M199" s="19"/>
       <c r="N199" s="20"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="16"/>
       <c r="B200" s="17"/>
       <c r="C200" s="17"/>
@@ -5283,7 +6250,7 @@
       <c r="M200" s="19"/>
       <c r="N200" s="20"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="16"/>
       <c r="B201" s="17"/>
       <c r="C201" s="17"/>
@@ -5305,7 +6272,7 @@
       <c r="M201" s="19"/>
       <c r="N201" s="20"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="16"/>
       <c r="B202" s="17"/>
       <c r="C202" s="17"/>
@@ -5327,7 +6294,7 @@
       <c r="M202" s="19"/>
       <c r="N202" s="20"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="16"/>
       <c r="B203" s="17"/>
       <c r="C203" s="17"/>
@@ -5349,7 +6316,7 @@
       <c r="M203" s="19"/>
       <c r="N203" s="20"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="16"/>
       <c r="B204" s="17"/>
       <c r="C204" s="17"/>
@@ -5371,7 +6338,7 @@
       <c r="M204" s="19"/>
       <c r="N204" s="20"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="16"/>
       <c r="B205" s="17"/>
       <c r="C205" s="17"/>
@@ -5393,7 +6360,7 @@
       <c r="M205" s="19"/>
       <c r="N205" s="20"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="16"/>
       <c r="B206" s="17"/>
       <c r="C206" s="17"/>
@@ -5415,7 +6382,7 @@
       <c r="M206" s="19"/>
       <c r="N206" s="20"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="16"/>
       <c r="B207" s="17"/>
       <c r="C207" s="17"/>
@@ -5437,7 +6404,7 @@
       <c r="M207" s="19"/>
       <c r="N207" s="20"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="16"/>
       <c r="B208" s="17"/>
       <c r="C208" s="17"/>
@@ -5459,7 +6426,7 @@
       <c r="M208" s="19"/>
       <c r="N208" s="20"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="16"/>
       <c r="B209" s="17"/>
       <c r="C209" s="17"/>
@@ -5481,7 +6448,7 @@
       <c r="M209" s="19"/>
       <c r="N209" s="20"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="16"/>
       <c r="B210" s="17"/>
       <c r="C210" s="17"/>
@@ -5503,7 +6470,7 @@
       <c r="M210" s="19"/>
       <c r="N210" s="20"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="16"/>
       <c r="B211" s="17"/>
       <c r="C211" s="17"/>
@@ -5525,7 +6492,7 @@
       <c r="M211" s="19"/>
       <c r="N211" s="20"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="16"/>
       <c r="B212" s="17"/>
       <c r="C212" s="17"/>
@@ -5547,7 +6514,7 @@
       <c r="M212" s="19"/>
       <c r="N212" s="20"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="16"/>
       <c r="B213" s="17"/>
       <c r="C213" s="17"/>
@@ -5569,7 +6536,7 @@
       <c r="M213" s="19"/>
       <c r="N213" s="20"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="16"/>
       <c r="B214" s="17"/>
       <c r="C214" s="17"/>
@@ -5591,7 +6558,7 @@
       <c r="M214" s="19"/>
       <c r="N214" s="20"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="16"/>
       <c r="B215" s="17"/>
       <c r="C215" s="17"/>
@@ -5613,7 +6580,7 @@
       <c r="M215" s="19"/>
       <c r="N215" s="20"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="16"/>
       <c r="B216" s="17"/>
       <c r="C216" s="17"/>
@@ -5635,7 +6602,7 @@
       <c r="M216" s="19"/>
       <c r="N216" s="20"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="16"/>
       <c r="B217" s="17"/>
       <c r="C217" s="17"/>
@@ -5657,7 +6624,7 @@
       <c r="M217" s="19"/>
       <c r="N217" s="20"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="16"/>
       <c r="B218" s="17"/>
       <c r="C218" s="17"/>
@@ -5679,7 +6646,7 @@
       <c r="M218" s="19"/>
       <c r="N218" s="20"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="16"/>
       <c r="B219" s="17"/>
       <c r="C219" s="17"/>
@@ -5701,7 +6668,7 @@
       <c r="M219" s="19"/>
       <c r="N219" s="20"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="16"/>
       <c r="B220" s="17"/>
       <c r="C220" s="17"/>
@@ -5723,7 +6690,7 @@
       <c r="M220" s="19"/>
       <c r="N220" s="20"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="16"/>
       <c r="B221" s="17"/>
       <c r="C221" s="17"/>
@@ -5745,7 +6712,7 @@
       <c r="M221" s="19"/>
       <c r="N221" s="20"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="16"/>
       <c r="B222" s="17"/>
       <c r="C222" s="17"/>
@@ -5767,7 +6734,7 @@
       <c r="M222" s="19"/>
       <c r="N222" s="20"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="16"/>
       <c r="B223" s="17"/>
       <c r="C223" s="17"/>
@@ -5789,7 +6756,7 @@
       <c r="M223" s="19"/>
       <c r="N223" s="20"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="16"/>
       <c r="B224" s="17"/>
       <c r="C224" s="17"/>
@@ -5811,7 +6778,7 @@
       <c r="M224" s="19"/>
       <c r="N224" s="20"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="16"/>
       <c r="B225" s="17"/>
       <c r="C225" s="17"/>
@@ -5833,7 +6800,7 @@
       <c r="M225" s="19"/>
       <c r="N225" s="20"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="16"/>
       <c r="B226" s="17"/>
       <c r="C226" s="17"/>
@@ -5855,7 +6822,7 @@
       <c r="M226" s="19"/>
       <c r="N226" s="20"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="16"/>
       <c r="B227" s="17"/>
       <c r="C227" s="17"/>
@@ -5877,7 +6844,7 @@
       <c r="M227" s="19"/>
       <c r="N227" s="20"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="16"/>
       <c r="B228" s="17"/>
       <c r="C228" s="17"/>
@@ -5899,7 +6866,7 @@
       <c r="M228" s="19"/>
       <c r="N228" s="20"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="16"/>
       <c r="B229" s="17"/>
       <c r="C229" s="17"/>
@@ -5921,7 +6888,7 @@
       <c r="M229" s="19"/>
       <c r="N229" s="20"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="16"/>
       <c r="B230" s="17"/>
       <c r="C230" s="17"/>
@@ -5943,7 +6910,7 @@
       <c r="M230" s="19"/>
       <c r="N230" s="20"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="16"/>
       <c r="B231" s="17"/>
       <c r="C231" s="17"/>
@@ -5965,7 +6932,7 @@
       <c r="M231" s="19"/>
       <c r="N231" s="20"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="16"/>
       <c r="B232" s="17"/>
       <c r="C232" s="17"/>
@@ -5987,7 +6954,7 @@
       <c r="M232" s="19"/>
       <c r="N232" s="20"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="16"/>
       <c r="B233" s="17"/>
       <c r="C233" s="17"/>
@@ -6009,7 +6976,7 @@
       <c r="M233" s="19"/>
       <c r="N233" s="20"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="16"/>
       <c r="B234" s="17"/>
       <c r="C234" s="17"/>
@@ -6031,7 +6998,7 @@
       <c r="M234" s="19"/>
       <c r="N234" s="20"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="16"/>
       <c r="B235" s="17"/>
       <c r="C235" s="17"/>
@@ -6053,7 +7020,7 @@
       <c r="M235" s="19"/>
       <c r="N235" s="20"/>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="16"/>
       <c r="B236" s="17"/>
       <c r="C236" s="17"/>
@@ -6075,7 +7042,7 @@
       <c r="M236" s="19"/>
       <c r="N236" s="20"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="16"/>
       <c r="B237" s="17"/>
       <c r="C237" s="17"/>
@@ -6097,7 +7064,7 @@
       <c r="M237" s="19"/>
       <c r="N237" s="20"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="16"/>
       <c r="B238" s="17"/>
       <c r="C238" s="17"/>
@@ -6119,7 +7086,7 @@
       <c r="M238" s="19"/>
       <c r="N238" s="20"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="16"/>
       <c r="B239" s="17"/>
       <c r="C239" s="17"/>
@@ -6141,7 +7108,7 @@
       <c r="M239" s="19"/>
       <c r="N239" s="20"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="16"/>
       <c r="B240" s="17"/>
       <c r="C240" s="17"/>
@@ -6163,7 +7130,7 @@
       <c r="M240" s="19"/>
       <c r="N240" s="20"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="16"/>
       <c r="B241" s="17"/>
       <c r="C241" s="17"/>
@@ -6185,7 +7152,7 @@
       <c r="M241" s="19"/>
       <c r="N241" s="20"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="16"/>
       <c r="B242" s="17"/>
       <c r="C242" s="17"/>
@@ -6207,7 +7174,7 @@
       <c r="M242" s="19"/>
       <c r="N242" s="20"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="16"/>
       <c r="B243" s="17"/>
       <c r="C243" s="17"/>
@@ -6229,7 +7196,7 @@
       <c r="M243" s="19"/>
       <c r="N243" s="20"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="16"/>
       <c r="B244" s="17"/>
       <c r="C244" s="17"/>
@@ -6251,7 +7218,7 @@
       <c r="M244" s="19"/>
       <c r="N244" s="20"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="16"/>
       <c r="B245" s="17"/>
       <c r="C245" s="17"/>
@@ -6273,7 +7240,7 @@
       <c r="M245" s="19"/>
       <c r="N245" s="20"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="16"/>
       <c r="B246" s="17"/>
       <c r="C246" s="17"/>
@@ -6295,7 +7262,7 @@
       <c r="M246" s="19"/>
       <c r="N246" s="20"/>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="16"/>
       <c r="B247" s="17"/>
       <c r="C247" s="17"/>
@@ -6317,7 +7284,7 @@
       <c r="M247" s="19"/>
       <c r="N247" s="20"/>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="16"/>
       <c r="B248" s="17"/>
       <c r="C248" s="17"/>
@@ -6339,7 +7306,7 @@
       <c r="M248" s="19"/>
       <c r="N248" s="20"/>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="16"/>
       <c r="B249" s="17"/>
       <c r="C249" s="17"/>
@@ -6361,7 +7328,7 @@
       <c r="M249" s="19"/>
       <c r="N249" s="20"/>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="16"/>
       <c r="B250" s="17"/>
       <c r="C250" s="17"/>
@@ -6383,7 +7350,7 @@
       <c r="M250" s="19"/>
       <c r="N250" s="20"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="16"/>
       <c r="B251" s="17"/>
       <c r="C251" s="17"/>
@@ -6405,7 +7372,7 @@
       <c r="M251" s="19"/>
       <c r="N251" s="20"/>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="16"/>
       <c r="B252" s="17"/>
       <c r="C252" s="17"/>
@@ -6427,7 +7394,7 @@
       <c r="M252" s="19"/>
       <c r="N252" s="20"/>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="16"/>
       <c r="B253" s="17"/>
       <c r="C253" s="17"/>
@@ -6449,7 +7416,7 @@
       <c r="M253" s="19"/>
       <c r="N253" s="20"/>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="16"/>
       <c r="B254" s="17"/>
       <c r="C254" s="17"/>
@@ -6471,7 +7438,7 @@
       <c r="M254" s="19"/>
       <c r="N254" s="20"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="16"/>
       <c r="B255" s="17"/>
       <c r="C255" s="17"/>
@@ -6493,7 +7460,7 @@
       <c r="M255" s="19"/>
       <c r="N255" s="20"/>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="16"/>
       <c r="B256" s="17"/>
       <c r="C256" s="17"/>
@@ -6515,7 +7482,7 @@
       <c r="M256" s="19"/>
       <c r="N256" s="20"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="16"/>
       <c r="B257" s="17"/>
       <c r="C257" s="17"/>
@@ -6537,7 +7504,7 @@
       <c r="M257" s="19"/>
       <c r="N257" s="20"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="16"/>
       <c r="B258" s="17"/>
       <c r="C258" s="17"/>
@@ -6559,7 +7526,7 @@
       <c r="M258" s="19"/>
       <c r="N258" s="20"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="16"/>
       <c r="B259" s="17"/>
       <c r="C259" s="17"/>
@@ -6581,7 +7548,7 @@
       <c r="M259" s="19"/>
       <c r="N259" s="20"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="16"/>
       <c r="B260" s="17"/>
       <c r="C260" s="17"/>
@@ -6603,7 +7570,7 @@
       <c r="M260" s="19"/>
       <c r="N260" s="20"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="16"/>
       <c r="B261" s="17"/>
       <c r="C261" s="17"/>
@@ -6625,7 +7592,7 @@
       <c r="M261" s="19"/>
       <c r="N261" s="20"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="16"/>
       <c r="B262" s="17"/>
       <c r="C262" s="17"/>
@@ -6647,7 +7614,7 @@
       <c r="M262" s="19"/>
       <c r="N262" s="20"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="16"/>
       <c r="B263" s="17"/>
       <c r="C263" s="17"/>
@@ -6669,7 +7636,7 @@
       <c r="M263" s="19"/>
       <c r="N263" s="20"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="16"/>
       <c r="B264" s="17"/>
       <c r="C264" s="17"/>
@@ -6691,7 +7658,7 @@
       <c r="M264" s="19"/>
       <c r="N264" s="20"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="16"/>
       <c r="B265" s="17"/>
       <c r="C265" s="17"/>
@@ -6713,7 +7680,7 @@
       <c r="M265" s="19"/>
       <c r="N265" s="20"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="16"/>
       <c r="B266" s="17"/>
       <c r="C266" s="17"/>
@@ -6735,7 +7702,7 @@
       <c r="M266" s="19"/>
       <c r="N266" s="20"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="16"/>
       <c r="B267" s="17"/>
       <c r="C267" s="17"/>
@@ -6757,7 +7724,7 @@
       <c r="M267" s="19"/>
       <c r="N267" s="20"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="16"/>
       <c r="B268" s="17"/>
       <c r="C268" s="17"/>
@@ -6779,7 +7746,7 @@
       <c r="M268" s="19"/>
       <c r="N268" s="20"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="16"/>
       <c r="B269" s="17"/>
       <c r="C269" s="17"/>
@@ -6801,7 +7768,7 @@
       <c r="M269" s="19"/>
       <c r="N269" s="20"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="16"/>
       <c r="B270" s="17"/>
       <c r="C270" s="17"/>
@@ -6823,7 +7790,7 @@
       <c r="M270" s="19"/>
       <c r="N270" s="20"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="16"/>
       <c r="B271" s="17"/>
       <c r="C271" s="17"/>
@@ -6845,7 +7812,7 @@
       <c r="M271" s="19"/>
       <c r="N271" s="20"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="16"/>
       <c r="B272" s="17"/>
       <c r="C272" s="17"/>
@@ -6867,7 +7834,7 @@
       <c r="M272" s="19"/>
       <c r="N272" s="20"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="16"/>
       <c r="B273" s="17"/>
       <c r="C273" s="17"/>
@@ -6889,7 +7856,7 @@
       <c r="M273" s="19"/>
       <c r="N273" s="20"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="16"/>
       <c r="B274" s="17"/>
       <c r="C274" s="17"/>
@@ -6911,7 +7878,7 @@
       <c r="M274" s="19"/>
       <c r="N274" s="20"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="16"/>
       <c r="B275" s="17"/>
       <c r="C275" s="17"/>
@@ -6933,7 +7900,7 @@
       <c r="M275" s="19"/>
       <c r="N275" s="20"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="16"/>
       <c r="B276" s="17"/>
       <c r="C276" s="17"/>
@@ -6955,7 +7922,7 @@
       <c r="M276" s="19"/>
       <c r="N276" s="20"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="16"/>
       <c r="B277" s="17"/>
       <c r="C277" s="17"/>
@@ -6977,7 +7944,7 @@
       <c r="M277" s="19"/>
       <c r="N277" s="20"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="16"/>
       <c r="B278" s="17"/>
       <c r="C278" s="17"/>
@@ -6999,7 +7966,7 @@
       <c r="M278" s="19"/>
       <c r="N278" s="20"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="16"/>
       <c r="B279" s="17"/>
       <c r="C279" s="17"/>
@@ -7021,7 +7988,7 @@
       <c r="M279" s="19"/>
       <c r="N279" s="20"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="16"/>
       <c r="B280" s="17"/>
       <c r="C280" s="17"/>
@@ -7043,7 +8010,7 @@
       <c r="M280" s="19"/>
       <c r="N280" s="20"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="16"/>
       <c r="B281" s="17"/>
       <c r="C281" s="17"/>
@@ -7065,7 +8032,7 @@
       <c r="M281" s="19"/>
       <c r="N281" s="20"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="16"/>
       <c r="B282" s="17"/>
       <c r="C282" s="17"/>
@@ -7087,7 +8054,7 @@
       <c r="M282" s="19"/>
       <c r="N282" s="20"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="16"/>
       <c r="B283" s="17"/>
       <c r="C283" s="17"/>
@@ -7109,7 +8076,7 @@
       <c r="M283" s="19"/>
       <c r="N283" s="20"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="16"/>
       <c r="B284" s="17"/>
       <c r="C284" s="17"/>
@@ -7131,7 +8098,7 @@
       <c r="M284" s="19"/>
       <c r="N284" s="20"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="16"/>
       <c r="B285" s="17"/>
       <c r="C285" s="17"/>
@@ -7153,7 +8120,7 @@
       <c r="M285" s="19"/>
       <c r="N285" s="20"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="16"/>
       <c r="B286" s="17"/>
       <c r="C286" s="17"/>
@@ -7175,7 +8142,7 @@
       <c r="M286" s="19"/>
       <c r="N286" s="20"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="16"/>
       <c r="B287" s="17"/>
       <c r="C287" s="17"/>
@@ -7197,7 +8164,7 @@
       <c r="M287" s="19"/>
       <c r="N287" s="20"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="16"/>
       <c r="B288" s="17"/>
       <c r="C288" s="17"/>
@@ -7219,7 +8186,7 @@
       <c r="M288" s="19"/>
       <c r="N288" s="20"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="16"/>
       <c r="B289" s="17"/>
       <c r="C289" s="17"/>
@@ -7241,7 +8208,7 @@
       <c r="M289" s="19"/>
       <c r="N289" s="20"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="16"/>
       <c r="B290" s="17"/>
       <c r="C290" s="17"/>
@@ -7263,7 +8230,7 @@
       <c r="M290" s="19"/>
       <c r="N290" s="20"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="16"/>
       <c r="B291" s="17"/>
       <c r="C291" s="17"/>
@@ -7285,7 +8252,7 @@
       <c r="M291" s="19"/>
       <c r="N291" s="20"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="16"/>
       <c r="B292" s="17"/>
       <c r="C292" s="17"/>
@@ -7307,7 +8274,7 @@
       <c r="M292" s="19"/>
       <c r="N292" s="20"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="16"/>
       <c r="B293" s="17"/>
       <c r="C293" s="17"/>
@@ -7329,7 +8296,7 @@
       <c r="M293" s="19"/>
       <c r="N293" s="20"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="16"/>
       <c r="B294" s="17"/>
       <c r="C294" s="17"/>
@@ -7351,7 +8318,7 @@
       <c r="M294" s="19"/>
       <c r="N294" s="20"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="16"/>
       <c r="B295" s="17"/>
       <c r="C295" s="17"/>
@@ -7373,7 +8340,7 @@
       <c r="M295" s="19"/>
       <c r="N295" s="20"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="16"/>
       <c r="B296" s="17"/>
       <c r="C296" s="17"/>
@@ -7395,7 +8362,7 @@
       <c r="M296" s="19"/>
       <c r="N296" s="20"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="16"/>
       <c r="B297" s="17"/>
       <c r="C297" s="17"/>
@@ -7417,7 +8384,7 @@
       <c r="M297" s="19"/>
       <c r="N297" s="20"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="16"/>
       <c r="B298" s="17"/>
       <c r="C298" s="17"/>
@@ -7439,7 +8406,7 @@
       <c r="M298" s="19"/>
       <c r="N298" s="20"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="16"/>
       <c r="B299" s="17"/>
       <c r="C299" s="17"/>
@@ -7461,7 +8428,7 @@
       <c r="M299" s="19"/>
       <c r="N299" s="20"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="16"/>
       <c r="B300" s="17"/>
       <c r="C300" s="17"/>
@@ -7483,7 +8450,7 @@
       <c r="M300" s="19"/>
       <c r="N300" s="20"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="16"/>
       <c r="B301" s="17"/>
       <c r="C301" s="17"/>
@@ -7505,7 +8472,7 @@
       <c r="M301" s="19"/>
       <c r="N301" s="20"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="16"/>
       <c r="B302" s="17"/>
       <c r="C302" s="17"/>
@@ -7527,7 +8494,7 @@
       <c r="M302" s="19"/>
       <c r="N302" s="20"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="16"/>
       <c r="B303" s="17"/>
       <c r="C303" s="17"/>
@@ -7549,7 +8516,7 @@
       <c r="M303" s="19"/>
       <c r="N303" s="20"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="16"/>
       <c r="B304" s="17"/>
       <c r="C304" s="17"/>
@@ -7571,7 +8538,7 @@
       <c r="M304" s="19"/>
       <c r="N304" s="20"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="16"/>
       <c r="B305" s="17"/>
       <c r="C305" s="17"/>
@@ -7593,7 +8560,7 @@
       <c r="M305" s="19"/>
       <c r="N305" s="20"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="16"/>
       <c r="B306" s="17"/>
       <c r="C306" s="17"/>
@@ -7615,7 +8582,7 @@
       <c r="M306" s="19"/>
       <c r="N306" s="20"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="16"/>
       <c r="B307" s="17"/>
       <c r="C307" s="17"/>
@@ -7637,7 +8604,7 @@
       <c r="M307" s="19"/>
       <c r="N307" s="20"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="16"/>
       <c r="B308" s="17"/>
       <c r="C308" s="17"/>
@@ -7659,7 +8626,7 @@
       <c r="M308" s="19"/>
       <c r="N308" s="20"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="16"/>
       <c r="B309" s="17"/>
       <c r="C309" s="17"/>
@@ -7681,7 +8648,7 @@
       <c r="M309" s="19"/>
       <c r="N309" s="20"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="16"/>
       <c r="B310" s="17"/>
       <c r="C310" s="17"/>
@@ -7703,7 +8670,7 @@
       <c r="M310" s="19"/>
       <c r="N310" s="20"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="16"/>
       <c r="B311" s="17"/>
       <c r="C311" s="17"/>
@@ -7725,7 +8692,7 @@
       <c r="M311" s="19"/>
       <c r="N311" s="20"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="16"/>
       <c r="B312" s="17"/>
       <c r="C312" s="17"/>
@@ -7747,7 +8714,7 @@
       <c r="M312" s="19"/>
       <c r="N312" s="20"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="16"/>
       <c r="B313" s="17"/>
       <c r="C313" s="17"/>
@@ -7769,7 +8736,7 @@
       <c r="M313" s="19"/>
       <c r="N313" s="20"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="16"/>
       <c r="B314" s="17"/>
       <c r="C314" s="17"/>
@@ -7791,7 +8758,7 @@
       <c r="M314" s="19"/>
       <c r="N314" s="20"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="16"/>
       <c r="B315" s="17"/>
       <c r="C315" s="17"/>
@@ -7813,7 +8780,7 @@
       <c r="M315" s="19"/>
       <c r="N315" s="20"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="16"/>
       <c r="B316" s="17"/>
       <c r="C316" s="17"/>
@@ -7835,7 +8802,7 @@
       <c r="M316" s="19"/>
       <c r="N316" s="20"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="16"/>
       <c r="B317" s="17"/>
       <c r="C317" s="17"/>
@@ -7857,7 +8824,7 @@
       <c r="M317" s="19"/>
       <c r="N317" s="20"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="16"/>
       <c r="B318" s="17"/>
       <c r="C318" s="17"/>
@@ -7879,7 +8846,7 @@
       <c r="M318" s="19"/>
       <c r="N318" s="20"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="16"/>
       <c r="B319" s="17"/>
       <c r="C319" s="17"/>
@@ -7901,7 +8868,7 @@
       <c r="M319" s="19"/>
       <c r="N319" s="20"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="16"/>
       <c r="B320" s="17"/>
       <c r="C320" s="17"/>
@@ -7923,7 +8890,7 @@
       <c r="M320" s="19"/>
       <c r="N320" s="20"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="16"/>
       <c r="B321" s="17"/>
       <c r="C321" s="17"/>
@@ -7945,7 +8912,7 @@
       <c r="M321" s="19"/>
       <c r="N321" s="20"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="16"/>
       <c r="B322" s="17"/>
       <c r="C322" s="17"/>
@@ -7967,7 +8934,7 @@
       <c r="M322" s="19"/>
       <c r="N322" s="20"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="16"/>
       <c r="B323" s="17"/>
       <c r="C323" s="17"/>
@@ -7989,7 +8956,7 @@
       <c r="M323" s="19"/>
       <c r="N323" s="20"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="16"/>
       <c r="B324" s="17"/>
       <c r="C324" s="17"/>
@@ -8011,7 +8978,7 @@
       <c r="M324" s="19"/>
       <c r="N324" s="20"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="16"/>
       <c r="B325" s="17"/>
       <c r="C325" s="17"/>
@@ -8033,7 +9000,7 @@
       <c r="M325" s="19"/>
       <c r="N325" s="20"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="16"/>
       <c r="B326" s="17"/>
       <c r="C326" s="17"/>
@@ -8055,7 +9022,7 @@
       <c r="M326" s="19"/>
       <c r="N326" s="20"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="16"/>
       <c r="B327" s="17"/>
       <c r="C327" s="17"/>
@@ -8077,7 +9044,7 @@
       <c r="M327" s="19"/>
       <c r="N327" s="20"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="16"/>
       <c r="B328" s="17"/>
       <c r="C328" s="17"/>
@@ -8099,7 +9066,7 @@
       <c r="M328" s="19"/>
       <c r="N328" s="20"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="16"/>
       <c r="B329" s="17"/>
       <c r="C329" s="17"/>
@@ -8121,7 +9088,7 @@
       <c r="M329" s="19"/>
       <c r="N329" s="20"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="16"/>
       <c r="B330" s="17"/>
       <c r="C330" s="17"/>
@@ -8143,7 +9110,7 @@
       <c r="M330" s="19"/>
       <c r="N330" s="20"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="16"/>
       <c r="B331" s="17"/>
       <c r="C331" s="17"/>
@@ -8165,7 +9132,7 @@
       <c r="M331" s="19"/>
       <c r="N331" s="20"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="16"/>
       <c r="B332" s="17"/>
       <c r="C332" s="17"/>
@@ -8187,7 +9154,7 @@
       <c r="M332" s="19"/>
       <c r="N332" s="20"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="16"/>
       <c r="B333" s="17"/>
       <c r="C333" s="17"/>
@@ -8209,7 +9176,7 @@
       <c r="M333" s="19"/>
       <c r="N333" s="20"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="16"/>
       <c r="B334" s="17"/>
       <c r="C334" s="17"/>
@@ -8231,7 +9198,7 @@
       <c r="M334" s="19"/>
       <c r="N334" s="20"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="16"/>
       <c r="B335" s="17"/>
       <c r="C335" s="17"/>
@@ -8253,7 +9220,7 @@
       <c r="M335" s="19"/>
       <c r="N335" s="20"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="16"/>
       <c r="B336" s="17"/>
       <c r="C336" s="17"/>
@@ -8275,7 +9242,7 @@
       <c r="M336" s="19"/>
       <c r="N336" s="20"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="16"/>
       <c r="B337" s="17"/>
       <c r="C337" s="17"/>
@@ -8297,7 +9264,7 @@
       <c r="M337" s="19"/>
       <c r="N337" s="20"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="16"/>
       <c r="B338" s="17"/>
       <c r="C338" s="17"/>
@@ -8319,7 +9286,7 @@
       <c r="M338" s="19"/>
       <c r="N338" s="20"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="16"/>
       <c r="B339" s="17"/>
       <c r="C339" s="17"/>
@@ -8341,7 +9308,7 @@
       <c r="M339" s="19"/>
       <c r="N339" s="20"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="16"/>
       <c r="B340" s="17"/>
       <c r="C340" s="17"/>
@@ -8363,7 +9330,7 @@
       <c r="M340" s="19"/>
       <c r="N340" s="20"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="16"/>
       <c r="B341" s="17"/>
       <c r="C341" s="17"/>
@@ -8385,7 +9352,7 @@
       <c r="M341" s="19"/>
       <c r="N341" s="20"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="16"/>
       <c r="B342" s="17"/>
       <c r="C342" s="17"/>
@@ -8407,7 +9374,7 @@
       <c r="M342" s="19"/>
       <c r="N342" s="20"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="16"/>
       <c r="B343" s="17"/>
       <c r="C343" s="17"/>
@@ -8429,7 +9396,7 @@
       <c r="M343" s="19"/>
       <c r="N343" s="20"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="16"/>
       <c r="B344" s="17"/>
       <c r="C344" s="17"/>
@@ -8451,7 +9418,7 @@
       <c r="M344" s="19"/>
       <c r="N344" s="20"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="16"/>
       <c r="B345" s="17"/>
       <c r="C345" s="17"/>
@@ -8473,7 +9440,7 @@
       <c r="M345" s="19"/>
       <c r="N345" s="20"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="16"/>
       <c r="B346" s="17"/>
       <c r="C346" s="17"/>
@@ -8495,7 +9462,7 @@
       <c r="M346" s="19"/>
       <c r="N346" s="20"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="16"/>
       <c r="B347" s="17"/>
       <c r="C347" s="17"/>
@@ -8517,7 +9484,7 @@
       <c r="M347" s="19"/>
       <c r="N347" s="20"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="16"/>
       <c r="B348" s="17"/>
       <c r="C348" s="17"/>
@@ -8539,7 +9506,7 @@
       <c r="M348" s="19"/>
       <c r="N348" s="20"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="16"/>
       <c r="B349" s="17"/>
       <c r="C349" s="17"/>
@@ -8561,7 +9528,7 @@
       <c r="M349" s="19"/>
       <c r="N349" s="20"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="16"/>
       <c r="B350" s="17"/>
       <c r="C350" s="17"/>
@@ -8583,7 +9550,7 @@
       <c r="M350" s="19"/>
       <c r="N350" s="20"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="16"/>
       <c r="B351" s="17"/>
       <c r="C351" s="17"/>
@@ -8605,7 +9572,7 @@
       <c r="M351" s="19"/>
       <c r="N351" s="20"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="16"/>
       <c r="B352" s="17"/>
       <c r="C352" s="17"/>
@@ -8627,7 +9594,7 @@
       <c r="M352" s="19"/>
       <c r="N352" s="20"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="16"/>
       <c r="B353" s="17"/>
       <c r="C353" s="17"/>
@@ -8649,7 +9616,7 @@
       <c r="M353" s="19"/>
       <c r="N353" s="20"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="16"/>
       <c r="B354" s="17"/>
       <c r="C354" s="17"/>
@@ -8671,7 +9638,7 @@
       <c r="M354" s="19"/>
       <c r="N354" s="20"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="16"/>
       <c r="B355" s="17"/>
       <c r="C355" s="17"/>
@@ -8693,7 +9660,7 @@
       <c r="M355" s="19"/>
       <c r="N355" s="20"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="16"/>
       <c r="B356" s="17"/>
       <c r="C356" s="17"/>
@@ -8715,7 +9682,7 @@
       <c r="M356" s="19"/>
       <c r="N356" s="20"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="16"/>
       <c r="B357" s="17"/>
       <c r="C357" s="17"/>
@@ -8737,7 +9704,7 @@
       <c r="M357" s="19"/>
       <c r="N357" s="20"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="16"/>
       <c r="B358" s="17"/>
       <c r="C358" s="17"/>
@@ -8759,7 +9726,7 @@
       <c r="M358" s="19"/>
       <c r="N358" s="20"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="16"/>
       <c r="B359" s="17"/>
       <c r="C359" s="17"/>
@@ -8781,7 +9748,7 @@
       <c r="M359" s="19"/>
       <c r="N359" s="20"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="16"/>
       <c r="B360" s="17"/>
       <c r="C360" s="17"/>
@@ -8803,7 +9770,7 @@
       <c r="M360" s="19"/>
       <c r="N360" s="20"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="16"/>
       <c r="B361" s="17"/>
       <c r="C361" s="17"/>
@@ -8825,7 +9792,7 @@
       <c r="M361" s="19"/>
       <c r="N361" s="20"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="16"/>
       <c r="B362" s="17"/>
       <c r="C362" s="17"/>
@@ -8847,7 +9814,7 @@
       <c r="M362" s="19"/>
       <c r="N362" s="20"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="16"/>
       <c r="B363" s="17"/>
       <c r="C363" s="17"/>
@@ -8869,7 +9836,7 @@
       <c r="M363" s="19"/>
       <c r="N363" s="20"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="16"/>
       <c r="B364" s="17"/>
       <c r="C364" s="17"/>
@@ -8891,7 +9858,7 @@
       <c r="M364" s="19"/>
       <c r="N364" s="20"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="16"/>
       <c r="B365" s="17"/>
       <c r="C365" s="17"/>
@@ -8913,7 +9880,7 @@
       <c r="M365" s="19"/>
       <c r="N365" s="20"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="16"/>
       <c r="B366" s="17"/>
       <c r="C366" s="17"/>
@@ -8935,7 +9902,7 @@
       <c r="M366" s="19"/>
       <c r="N366" s="20"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="16"/>
       <c r="B367" s="17"/>
       <c r="C367" s="17"/>
@@ -8957,7 +9924,7 @@
       <c r="M367" s="19"/>
       <c r="N367" s="20"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="16"/>
       <c r="B368" s="17"/>
       <c r="C368" s="17"/>
@@ -8979,7 +9946,7 @@
       <c r="M368" s="19"/>
       <c r="N368" s="20"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="16"/>
       <c r="B369" s="17"/>
       <c r="C369" s="17"/>
@@ -9001,7 +9968,7 @@
       <c r="M369" s="19"/>
       <c r="N369" s="20"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="16"/>
       <c r="B370" s="17"/>
       <c r="C370" s="17"/>
@@ -9023,7 +9990,7 @@
       <c r="M370" s="19"/>
       <c r="N370" s="20"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="16"/>
       <c r="B371" s="17"/>
       <c r="C371" s="17"/>
@@ -9045,7 +10012,7 @@
       <c r="M371" s="19"/>
       <c r="N371" s="20"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="16"/>
       <c r="B372" s="17"/>
       <c r="C372" s="17"/>
@@ -9067,7 +10034,7 @@
       <c r="M372" s="19"/>
       <c r="N372" s="20"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="16"/>
       <c r="B373" s="17"/>
       <c r="C373" s="17"/>
@@ -9089,7 +10056,7 @@
       <c r="M373" s="19"/>
       <c r="N373" s="20"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="16"/>
       <c r="B374" s="17"/>
       <c r="C374" s="17"/>
@@ -9111,7 +10078,7 @@
       <c r="M374" s="19"/>
       <c r="N374" s="20"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="16"/>
       <c r="B375" s="17"/>
       <c r="C375" s="17"/>
@@ -9133,7 +10100,7 @@
       <c r="M375" s="19"/>
       <c r="N375" s="20"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="16"/>
       <c r="B376" s="17"/>
       <c r="C376" s="17"/>
@@ -9155,7 +10122,7 @@
       <c r="M376" s="19"/>
       <c r="N376" s="20"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="16"/>
       <c r="B377" s="17"/>
       <c r="C377" s="17"/>
@@ -9177,7 +10144,7 @@
       <c r="M377" s="19"/>
       <c r="N377" s="20"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="16"/>
       <c r="B378" s="17"/>
       <c r="C378" s="17"/>
@@ -9199,7 +10166,7 @@
       <c r="M378" s="19"/>
       <c r="N378" s="20"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="16"/>
       <c r="B379" s="17"/>
       <c r="C379" s="17"/>
@@ -9221,7 +10188,7 @@
       <c r="M379" s="19"/>
       <c r="N379" s="20"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="16"/>
       <c r="B380" s="17"/>
       <c r="C380" s="17"/>
@@ -9243,7 +10210,7 @@
       <c r="M380" s="19"/>
       <c r="N380" s="20"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="16"/>
       <c r="B381" s="17"/>
       <c r="C381" s="17"/>
@@ -9265,7 +10232,7 @@
       <c r="M381" s="19"/>
       <c r="N381" s="20"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="16"/>
       <c r="B382" s="17"/>
       <c r="C382" s="17"/>
@@ -9287,7 +10254,7 @@
       <c r="M382" s="19"/>
       <c r="N382" s="20"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="16"/>
       <c r="B383" s="17"/>
       <c r="C383" s="17"/>
@@ -9309,7 +10276,7 @@
       <c r="M383" s="19"/>
       <c r="N383" s="20"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="16"/>
       <c r="B384" s="17"/>
       <c r="C384" s="17"/>
@@ -9331,7 +10298,7 @@
       <c r="M384" s="19"/>
       <c r="N384" s="20"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="16"/>
       <c r="B385" s="17"/>
       <c r="C385" s="17"/>
@@ -9353,7 +10320,7 @@
       <c r="M385" s="19"/>
       <c r="N385" s="20"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="16"/>
       <c r="B386" s="17"/>
       <c r="C386" s="17"/>
@@ -9375,7 +10342,7 @@
       <c r="M386" s="19"/>
       <c r="N386" s="20"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="16"/>
       <c r="B387" s="17"/>
       <c r="C387" s="17"/>
@@ -9397,7 +10364,7 @@
       <c r="M387" s="19"/>
       <c r="N387" s="20"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="16"/>
       <c r="B388" s="17"/>
       <c r="C388" s="17"/>
@@ -9419,7 +10386,7 @@
       <c r="M388" s="19"/>
       <c r="N388" s="20"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="16"/>
       <c r="B389" s="17"/>
       <c r="C389" s="17"/>
@@ -9441,7 +10408,7 @@
       <c r="M389" s="19"/>
       <c r="N389" s="20"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="16"/>
       <c r="B390" s="17"/>
       <c r="C390" s="17"/>
@@ -9463,7 +10430,7 @@
       <c r="M390" s="19"/>
       <c r="N390" s="20"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="16"/>
       <c r="B391" s="17"/>
       <c r="C391" s="17"/>
@@ -9485,7 +10452,7 @@
       <c r="M391" s="19"/>
       <c r="N391" s="20"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="16"/>
       <c r="B392" s="17"/>
       <c r="C392" s="17"/>
@@ -9507,7 +10474,7 @@
       <c r="M392" s="19"/>
       <c r="N392" s="20"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="16"/>
       <c r="B393" s="17"/>
       <c r="C393" s="17"/>
@@ -9529,7 +10496,7 @@
       <c r="M393" s="19"/>
       <c r="N393" s="20"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="16"/>
       <c r="B394" s="17"/>
       <c r="C394" s="17"/>
@@ -9551,7 +10518,7 @@
       <c r="M394" s="19"/>
       <c r="N394" s="20"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="16"/>
       <c r="B395" s="17"/>
       <c r="C395" s="17"/>
@@ -9573,7 +10540,7 @@
       <c r="M395" s="19"/>
       <c r="N395" s="20"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="16"/>
       <c r="B396" s="17"/>
       <c r="C396" s="17"/>
@@ -9595,7 +10562,7 @@
       <c r="M396" s="19"/>
       <c r="N396" s="20"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="16"/>
       <c r="B397" s="17"/>
       <c r="C397" s="17"/>
@@ -9617,7 +10584,7 @@
       <c r="M397" s="19"/>
       <c r="N397" s="20"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="16"/>
       <c r="B398" s="17"/>
       <c r="C398" s="17"/>
@@ -9639,7 +10606,7 @@
       <c r="M398" s="19"/>
       <c r="N398" s="20"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="16"/>
       <c r="B399" s="17"/>
       <c r="C399" s="17"/>
@@ -9661,7 +10628,7 @@
       <c r="M399" s="19"/>
       <c r="N399" s="20"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="16"/>
       <c r="B400" s="17"/>
       <c r="C400" s="17"/>
@@ -9683,7 +10650,7 @@
       <c r="M400" s="19"/>
       <c r="N400" s="20"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="16"/>
       <c r="B401" s="17"/>
       <c r="C401" s="17"/>
